--- a/data/trans_dic/P04D$aparatos-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P04D$aparatos-Edad-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, tiene aparatos de calefacción en su vivienda</t>
+          <t>Población que, al menos, tiene aparatos de calefacción en su vivienda (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>56,92; 65,93</t>
+          <t>56,93; 65,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>47,1; 57,07</t>
+          <t>47,06; 57,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53,16; 70,73</t>
+          <t>52,38; 69,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>59,99; 69,1</t>
+          <t>60,3; 69,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>46,45; 56,71</t>
+          <t>46,63; 56,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,65; 73,51</t>
+          <t>58,46; 72,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,63; 66,51</t>
+          <t>59,62; 66,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>48,72; 55,42</t>
+          <t>48,64; 55,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>58,57; 70,27</t>
+          <t>57,63; 69,66</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>58,23; 66,21</t>
+          <t>58,64; 66,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>47,03; 55,31</t>
+          <t>47,21; 55,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>58,66; 70,58</t>
+          <t>58,5; 70,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59,91; 67,5</t>
+          <t>60,15; 67,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>45,13; 53,31</t>
+          <t>44,72; 53,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,68; 64,06</t>
+          <t>31,73; 64,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,28; 65,6</t>
+          <t>60,23; 65,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>47,26; 52,86</t>
+          <t>47,34; 53,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>44,5; 65,08</t>
+          <t>43,85; 65,15</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>58,43; 66,03</t>
+          <t>58,24; 66,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>49,45; 57,28</t>
+          <t>49,14; 57,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>58,88; 67,62</t>
+          <t>58,68; 67,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>56,51; 64,54</t>
+          <t>56,84; 64,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>47,36; 55,11</t>
+          <t>47,24; 55,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>61,17; 75,09</t>
+          <t>61,16; 75,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>58,89; 64,17</t>
+          <t>58,89; 64,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>49,54; 54,93</t>
+          <t>49,55; 54,93</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>61,7; 69,99</t>
+          <t>61,33; 69,8</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>57,19; 65,81</t>
+          <t>57,69; 65,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>48,23; 56,47</t>
+          <t>48,24; 56,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,4; 62,6</t>
+          <t>18,2; 62,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>61,02; 69,18</t>
+          <t>60,44; 68,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>48,92; 57,07</t>
+          <t>49,07; 57,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,3; 68,34</t>
+          <t>59,05; 67,94</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,14; 66,03</t>
+          <t>60,19; 66,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>50,03; 55,71</t>
+          <t>49,86; 55,92</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30,14; 62,72</t>
+          <t>33,92; 62,85</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>57,22; 66,95</t>
+          <t>57,76; 67,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>45,39; 55,52</t>
+          <t>46,13; 55,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>63,0; 70,52</t>
+          <t>62,95; 70,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59,84; 69,15</t>
+          <t>59,42; 68,99</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>45,64; 55,36</t>
+          <t>46,01; 55,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>64,92; 70,73</t>
+          <t>65,21; 71,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>59,99; 67,11</t>
+          <t>60,3; 67,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>47,39; 54,41</t>
+          <t>47,44; 53,95</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>65,02; 69,89</t>
+          <t>65,04; 69,95</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>62,05; 73,61</t>
+          <t>62,18; 73,29</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>50,4; 61,12</t>
+          <t>50,21; 61,25</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>60,22; 68,19</t>
+          <t>60,06; 68,42</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>59,94; 70,53</t>
+          <t>60,24; 70,44</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>49,56; 60,06</t>
+          <t>48,97; 59,77</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>66,5; 90,85</t>
+          <t>66,44; 91,55</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>62,25; 69,8</t>
+          <t>62,59; 69,98</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>51,38; 58,75</t>
+          <t>51,21; 58,91</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>65,35; 87,55</t>
+          <t>65,4; 86,87</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>64,57; 77,19</t>
+          <t>64,26; 76,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>54,62; 65,98</t>
+          <t>54,63; 65,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>64,91; 73,72</t>
+          <t>64,69; 73,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>70,23; 79,93</t>
+          <t>70,36; 79,48</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>51,79; 63,11</t>
+          <t>52,34; 63,35</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,05; 76,19</t>
+          <t>70,0; 76,23</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,01; 77,49</t>
+          <t>69,74; 77,33</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>54,47; 62,9</t>
+          <t>54,37; 62,87</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>69,29; 74,38</t>
+          <t>69,02; 74,21</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>61,54; 64,9</t>
+          <t>61,53; 64,94</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>51,2; 54,69</t>
+          <t>51,3; 54,8</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>45,25; 64,75</t>
+          <t>46,61; 64,69</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>63,32; 66,68</t>
+          <t>63,38; 66,65</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>50,72; 53,94</t>
+          <t>50,48; 53,97</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>62,9; 72,14</t>
+          <t>63,16; 72,33</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>62,96; 65,36</t>
+          <t>62,94; 65,39</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>51,46; 53,81</t>
+          <t>51,47; 53,87</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>56,47; 66,81</t>
+          <t>55,51; 66,86</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, tiene aparatos de calefacción en su vivienda</t>
+          <t>Población que, al menos, tiene aparatos de calefacción en su vivienda (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>257465; 298191</t>
+          <t>257484; 296457</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>197575; 239403</t>
+          <t>197417; 239622</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>212558; 282811</t>
+          <t>209424; 278464</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>256924; 295936</t>
+          <t>258253; 296512</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>183829; 224420</t>
+          <t>184527; 225477</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>183698; 230220</t>
+          <t>183111; 228019</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>525118; 585706</t>
+          <t>524961; 582917</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>397195; 451782</t>
+          <t>396505; 452492</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>417602; 501029</t>
+          <t>410923; 496674</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>400118; 454888</t>
+          <t>402898; 454072</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>277701; 326588</t>
+          <t>278744; 326932</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>248452; 298959</t>
+          <t>247778; 299703</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>365588; 411946</t>
+          <t>367068; 414577</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>254350; 300450</t>
+          <t>252026; 300439</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>171964; 327053</t>
+          <t>162014; 327956</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>782067; 851099</t>
+          <t>781386; 854100</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>545430; 610021</t>
+          <t>546322; 612485</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>415657; 607928</t>
+          <t>409575; 608600</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>397842; 449627</t>
+          <t>396541; 451725</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>330844; 383278</t>
+          <t>328827; 384144</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>313863; 360428</t>
+          <t>312798; 358941</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>401086; 458022</t>
+          <t>403427; 455886</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>313244; 364480</t>
+          <t>312438; 364192</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>361600; 443842</t>
+          <t>361529; 447664</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>818964; 892425</t>
+          <t>818895; 891389</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>659058; 730879</t>
+          <t>659262; 730838</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>693613; 786841</t>
+          <t>689476; 784617</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>349590; 402274</t>
+          <t>352675; 402728</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>311594; 364848</t>
+          <t>311638; 364681</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>181141; 555733</t>
+          <t>161587; 557266</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>375349; 425490</t>
+          <t>371745; 423294</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>317512; 370443</t>
+          <t>318473; 370695</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>421605; 485849</t>
+          <t>419776; 482973</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>737591; 809762</t>
+          <t>738142; 811931</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>647929; 721568</t>
+          <t>645730; 724253</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>481844; 1002759</t>
+          <t>542242; 1004826</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>245719; 287511</t>
+          <t>248049; 291275</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>216949; 265342</t>
+          <t>220443; 265020</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>352302; 394353</t>
+          <t>352028; 394275</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>267981; 309652</t>
+          <t>266072; 308935</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>226768; 275051</t>
+          <t>228609; 276140</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>354452; 386201</t>
+          <t>356040; 388678</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>526209; 588692</t>
+          <t>528999; 588715</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>461915; 530355</t>
+          <t>462401; 525846</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>718633; 772418</t>
+          <t>718857; 773098</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>192214; 228021</t>
+          <t>192614; 227036</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>168491; 204356</t>
+          <t>167853; 204774</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>221304; 250567</t>
+          <t>220716; 251425</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>212203; 249664</t>
+          <t>213245; 249363</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>187208; 226896</t>
+          <t>184985; 225770</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>403811; 551611</t>
+          <t>403438; 555883</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>413180; 463321</t>
+          <t>415470; 464484</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>365846; 418341</t>
+          <t>364695; 419485</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>636957; 853357</t>
+          <t>637477; 846737</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>160712; 192113</t>
+          <t>159923; 190967</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>140369; 169556</t>
+          <t>140394; 169330</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>183538; 208455</t>
+          <t>182916; 207634</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>273184; 310927</t>
+          <t>273682; 309146</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>207232; 252558</t>
+          <t>209459; 253492</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>297987; 324092</t>
+          <t>297772; 324249</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>446579; 494302</t>
+          <t>444849; 493232</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>357927; 413390</t>
+          <t>357320; 413161</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>490689; 526697</t>
+          <t>488733; 525537</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2104605; 2219363</t>
+          <t>2104221; 2220822</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1737791; 1856233</t>
+          <t>1741456; 1860158</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1562695; 2236086</t>
+          <t>1609846; 2234310</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2250375; 2369772</t>
+          <t>2252736; 2368984</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1797706; 1912004</t>
+          <t>1789234; 1913164</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2330217; 2672409</t>
+          <t>2339580; 2679549</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4390928; 4557754</t>
+          <t>4389541; 4560390</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>3570685; 3733500</t>
+          <t>3571319; 3737823</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>4041784; 4782236</t>
+          <t>3973335; 4786039</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P04D$aparatos-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P04D$aparatos-Edad-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>62,43%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>63,94%</t>
+          <t>64,26%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>56,93; 65,54</t>
+          <t>57,06; 66,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>47,06; 57,13</t>
+          <t>47,21; 57,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52,38; 69,65</t>
+          <t>55,65; 70,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>60,3; 69,24</t>
+          <t>60,23; 69,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>46,63; 56,97</t>
+          <t>46,88; 56,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,46; 72,8</t>
+          <t>58,04; 71,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,62; 66,2</t>
+          <t>59,87; 66,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>48,64; 55,51</t>
+          <t>48,61; 55,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>57,63; 69,66</t>
+          <t>58,7; 69,44</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>63,71%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>58,64; 66,09</t>
+          <t>58,46; 65,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>47,21; 55,37</t>
+          <t>47,18; 55,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>58,5; 70,76</t>
+          <t>58,43; 69,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60,15; 67,94</t>
+          <t>60,17; 67,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>44,72; 53,31</t>
+          <t>45,01; 53,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,73; 64,24</t>
+          <t>58,6; 67,41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,23; 65,83</t>
+          <t>60,2; 65,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>47,34; 53,07</t>
+          <t>47,15; 53,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>43,85; 65,15</t>
+          <t>59,43; 66,9</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>63,32%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>62,9%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>58,24; 66,34</t>
+          <t>58,38; 66,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>49,14; 57,41</t>
+          <t>49,34; 57,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>58,68; 67,34</t>
+          <t>59,26; 67,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>56,84; 64,23</t>
+          <t>57,17; 64,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>47,24; 55,07</t>
+          <t>47,69; 55,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>61,16; 75,73</t>
+          <t>58,64; 65,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>58,89; 64,1</t>
+          <t>58,72; 63,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>49,55; 54,93</t>
+          <t>49,6; 55,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>61,33; 69,8</t>
+          <t>60,1; 65,5</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>60,83%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>60,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>60,66%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>57,69; 65,88</t>
+          <t>57,18; 65,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>48,24; 56,45</t>
+          <t>48,25; 56,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,2; 62,77</t>
+          <t>56,96; 64,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>60,44; 68,82</t>
+          <t>60,87; 68,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>49,07; 57,11</t>
+          <t>48,88; 57,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,05; 67,94</t>
+          <t>57,65; 63,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,19; 66,21</t>
+          <t>60,34; 66,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>49,86; 55,92</t>
+          <t>49,86; 55,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>33,92; 62,85</t>
+          <t>58,29; 62,87</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>66,21%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>66,61%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>57,76; 67,83</t>
+          <t>57,97; 67,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>46,13; 55,45</t>
+          <t>45,8; 55,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>62,95; 70,5</t>
+          <t>62,17; 69,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59,42; 68,99</t>
+          <t>59,63; 69,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>46,01; 55,58</t>
+          <t>45,67; 55,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>65,21; 71,18</t>
+          <t>64,19; 69,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>60,3; 67,11</t>
+          <t>60,08; 66,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>47,44; 53,95</t>
+          <t>47,73; 54,27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>65,04; 69,95</t>
+          <t>64,16; 68,77</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>64,33%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>65,77%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>62,18; 73,29</t>
+          <t>61,23; 73,06</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>50,21; 61,25</t>
+          <t>50,53; 61,3</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>60,06; 68,42</t>
+          <t>59,36; 68,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>60,24; 70,44</t>
+          <t>60,04; 70,41</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>48,97; 59,77</t>
+          <t>49,61; 60,34</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>66,44; 91,55</t>
+          <t>63,99; 70,25</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>62,59; 69,98</t>
+          <t>62,48; 70,1</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>51,21; 58,91</t>
+          <t>51,32; 59,07</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>65,4; 86,87</t>
+          <t>62,76; 68,08</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>72,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>70,67%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>64,26; 76,73</t>
+          <t>64,49; 77,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>54,63; 65,89</t>
+          <t>55,25; 65,82</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>64,69; 73,43</t>
+          <t>63,67; 72,6</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>70,36; 79,48</t>
+          <t>70,38; 80,07</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>52,34; 63,35</t>
+          <t>52,13; 62,95</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,0; 76,23</t>
+          <t>69,32; 75,52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,74; 77,33</t>
+          <t>69,99; 77,32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>54,37; 62,87</t>
+          <t>54,42; 62,73</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>69,02; 74,21</t>
+          <t>67,94; 73,21</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>64,49%</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>61,53; 64,94</t>
+          <t>61,28; 64,94</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>51,3; 54,8</t>
+          <t>51,34; 54,78</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>46,61; 64,69</t>
+          <t>62,23; 65,79</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>63,38; 66,65</t>
+          <t>63,42; 66,71</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>50,48; 53,97</t>
+          <t>50,55; 54,0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>63,16; 72,33</t>
+          <t>63,58; 66,38</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>62,94; 65,39</t>
+          <t>62,95; 65,18</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>51,47; 53,87</t>
+          <t>51,39; 53,81</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>55,51; 66,86</t>
+          <t>63,44; 65,68</t>
         </is>
       </c>
     </row>
@@ -1707,7 +1707,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>249609</t>
+          <t>255591</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>206330</t>
+          <t>237318</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>455939</t>
+          <t>492910</t>
         </is>
       </c>
     </row>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>257484; 296457</t>
+          <t>258060; 301034</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>197417; 239622</t>
+          <t>198011; 240161</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>209424; 278464</t>
+          <t>225105; 286293</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>258253; 296512</t>
+          <t>257936; 296540</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>184527; 225477</t>
+          <t>185545; 222911</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>183111; 228019</t>
+          <t>210407; 260152</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>524961; 582917</t>
+          <t>527194; 584759</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>396505; 452492</t>
+          <t>396317; 454888</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>410923; 496674</t>
+          <t>450230; 532649</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>274938</t>
+          <t>305926</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>276381</t>
+          <t>316352</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>551319</t>
+          <t>622278</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>402898; 454072</t>
+          <t>401684; 452492</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>278744; 326932</t>
+          <t>278590; 326436</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>247778; 299703</t>
+          <t>278656; 332782</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>367068; 414577</t>
+          <t>367160; 413987</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>252026; 300439</t>
+          <t>253659; 301780</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>162014; 327956</t>
+          <t>292944; 337003</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>781386; 854100</t>
+          <t>780936; 850788</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>546322; 612485</t>
+          <t>544148; 613535</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>409575; 608600</t>
+          <t>580503; 653451</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>336129</t>
+          <t>390215</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>389212</t>
+          <t>388301</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>725342</t>
+          <t>778515</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>396541; 451725</t>
+          <t>397524; 450879</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>328827; 384144</t>
+          <t>330149; 382575</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>312798; 358941</t>
+          <t>365169; 416145</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>403427; 455886</t>
+          <t>405748; 455596</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>312438; 364192</t>
+          <t>315435; 365790</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>361529; 447664</t>
+          <t>364439; 406376</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>818895; 891389</t>
+          <t>816562; 889891</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>659262; 730838</t>
+          <t>659887; 733915</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>689476; 784617</t>
+          <t>743861; 810693</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>393115</t>
+          <t>426157</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>444743</t>
+          <t>444581</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>837858</t>
+          <t>870738</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>352675; 402728</t>
+          <t>349517; 400434</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>311638; 364681</t>
+          <t>311690; 363965</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>161587; 557266</t>
+          <t>399043; 453756</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>371745; 423294</t>
+          <t>374397; 423631</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>318473; 370695</t>
+          <t>317261; 372882</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>419776; 482973</t>
+          <t>423608; 465722</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>738142; 811931</t>
+          <t>739956; 810841</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>645730; 724253</t>
+          <t>645732; 721104</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>542242; 1004826</t>
+          <t>836673; 902479</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>372902</t>
+          <t>402108</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>372260</t>
+          <t>406677</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>745163</t>
+          <t>808785</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>248049; 291275</t>
+          <t>248945; 289620</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>220443; 265020</t>
+          <t>218866; 266389</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>352028; 394275</t>
+          <t>377565; 422665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>266072; 308935</t>
+          <t>267002; 309749</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>228609; 276140</t>
+          <t>226900; 275381</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>356040; 388678</t>
+          <t>389546; 424424</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>528999; 588715</t>
+          <t>527011; 587358</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>462401; 525846</t>
+          <t>465269; 528983</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>718857; 773098</t>
+          <t>779037; 835016</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>236393</t>
+          <t>260548</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>477060</t>
+          <t>294612</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>713453</t>
+          <t>555160</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>192614; 227036</t>
+          <t>189671; 226326</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>167853; 204774</t>
+          <t>168936; 204932</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>220716; 251425</t>
+          <t>241114; 277297</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>213245; 249363</t>
+          <t>212539; 249231</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>184985; 225770</t>
+          <t>187404; 227923</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>403438; 555883</t>
+          <t>280258; 307636</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>415470; 464484</t>
+          <t>414718; 465309</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>364695; 419485</t>
+          <t>365457; 420604</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>637477; 846737</t>
+          <t>529826; 574726</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>195833</t>
+          <t>211888</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>311676</t>
+          <t>335359</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>507509</t>
+          <t>547247</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>159923; 190967</t>
+          <t>160498; 191652</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>140394; 169330</t>
+          <t>141994; 169162</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>182916; 207634</t>
+          <t>197503; 225195</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>273682; 309146</t>
+          <t>273750; 311445</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>209459; 253492</t>
+          <t>208622; 251922</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>297772; 324249</t>
+          <t>321744; 350538</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>444849; 493232</t>
+          <t>446474; 493208</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>357320; 413161</t>
+          <t>357604; 412269</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>488733; 525537</t>
+          <t>526117; 566911</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2058920</t>
+          <t>2252433</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2477662</t>
+          <t>2423199</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>4536582</t>
+          <t>4675633</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2104221; 2220822</t>
+          <t>2095498; 2220617</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1741456; 1860158</t>
+          <t>1742589; 1859574</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1609846; 2234310</t>
+          <t>2191626; 2316949</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2252736; 2368984</t>
+          <t>2254162; 2370938</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1789234; 1913164</t>
+          <t>1791631; 1914126</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2339580; 2679549</t>
+          <t>2370189; 2474243</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4389541; 4560390</t>
+          <t>4389925; 4545185</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>3571319; 3737823</t>
+          <t>3566002; 3733767</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3973335; 4786039</t>
+          <t>4598997; 4761793</t>
         </is>
       </c>
     </row>
